--- a/astro-site/public/dl/kit-tareas-bar/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/04-tareas-perfiles.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Head Bartender" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Bartender" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Barback" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Camarero Barra" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Head Bartender" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bartender" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barback" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camarero Barra" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Head Bartender'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Bartender'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Barback'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Camarero Barra'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -138,7 +143,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -160,68 +165,127 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="33">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="7" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -581,15 +645,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -597,6 +662,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -618,8 +684,33 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -628,18 +719,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -656,10 +747,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -684,7 +776,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -699,18 +791,16 @@
           <t xml:space="preserve">  Pre-Servicio</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -736,10 +826,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -765,10 +853,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="32" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -794,10 +880,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="32" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -823,10 +907,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="32" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -851,24 +933,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Servicio</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="30" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="32" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -894,10 +975,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="32" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -923,10 +1002,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="32" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -952,10 +1029,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="32" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -981,10 +1056,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="32" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1009,24 +1082,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre y Desarrollo</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="30" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="31" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="32" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1052,10 +1124,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1081,10 +1151,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="32" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1110,10 +1178,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="32" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1138,6 +1204,8 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
@@ -1146,17 +1214,19 @@
       </c>
       <c r="D26" s="19">
         <f>COUNTIF(F5:F24,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F26" s="19" t="n">
-        <v>14</v>
-      </c>
-    </row>
+      <c r="F26" s="19">
+        <f>COUNTIF(B5:B24,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
@@ -1164,13 +1234,17 @@
         </is>
       </c>
       <c r="B28" s="15" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="31" t="n"/>
       <c r="E28" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-    </row>
+      <c r="G28" s="31" t="n"/>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
@@ -1189,12 +1263,26 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B28:D28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1203,18 +1291,18 @@
   <sheetPr>
     <tabColor rgb="00FF8C00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1231,10 +1319,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1259,7 +1348,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1274,18 +1363,16 @@
           <t xml:space="preserve">  Pre-Servicio</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="23" t="n"/>
-      <c r="G5" s="23" t="n"/>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1311,10 +1398,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1340,10 +1425,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="32" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1369,10 +1452,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="32" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1398,10 +1479,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="32" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1426,24 +1505,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Servicio</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
-      <c r="G12" s="23" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="30" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="32" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1469,10 +1547,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="32" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1498,10 +1574,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="32" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1527,10 +1601,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="32" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1556,10 +1628,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="32" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1585,10 +1655,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="32" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1613,24 +1681,23 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="15" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="23" t="n"/>
-      <c r="F20" s="23" t="n"/>
-      <c r="G20" s="23" t="n"/>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="30" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="31" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1656,10 +1723,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="32" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1685,10 +1750,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="32" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1713,6 +1776,8 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
@@ -1721,17 +1786,19 @@
       </c>
       <c r="D26" s="19">
         <f>COUNTIF(F5:F24,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F26" s="19" t="n">
-        <v>14</v>
-      </c>
-    </row>
+      <c r="F26" s="19">
+        <f>COUNTIF(B5:B24,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
@@ -1739,13 +1806,17 @@
         </is>
       </c>
       <c r="B28" s="15" t="n"/>
+      <c r="C28" s="30" t="n"/>
+      <c r="D28" s="31" t="n"/>
       <c r="E28" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-    </row>
+      <c r="G28" s="31" t="n"/>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
@@ -1764,12 +1835,26 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B28:D28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1778,18 +1863,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1806,10 +1891,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1834,7 +1920,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1849,18 +1935,16 @@
           <t xml:space="preserve">  Soporte Continuo</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="23" t="n"/>
-      <c r="G5" s="23" t="n"/>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1886,10 +1970,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1915,10 +1997,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="32" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1944,10 +2024,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="32" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1973,10 +2051,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="32" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2002,10 +2078,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="32" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2031,10 +2105,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="32" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -2060,10 +2132,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="32" t="n">
+        <v>8</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -2088,24 +2158,23 @@
       <c r="F13" s="14" t="n"/>
       <c r="G13" s="15" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Limpieza</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="26" t="n"/>
-      <c r="G15" s="26" t="n"/>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="31" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="32" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2131,10 +2200,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="32" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2160,10 +2227,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="32" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2189,10 +2254,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -2218,10 +2281,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="32" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2246,6 +2307,8 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="15" t="n"/>
     </row>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
@@ -2254,17 +2317,19 @@
       </c>
       <c r="D23" s="19">
         <f>COUNTIF(F5:F21,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F23" s="19" t="n">
-        <v>13</v>
-      </c>
-    </row>
+      <c r="F23" s="19">
+        <f>COUNTIF(B5:B21,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
@@ -2272,13 +2337,17 @@
         </is>
       </c>
       <c r="B25" s="15" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="31" t="n"/>
       <c r="E25" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F25" s="15" t="n"/>
-    </row>
+      <c r="G25" s="31" t="n"/>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
         <is>
@@ -2296,12 +2365,26 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B25:D25"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2310,18 +2393,18 @@
   <sheetPr>
     <tabColor rgb="002196F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2338,10 +2421,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2366,7 +2450,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2381,18 +2465,16 @@
           <t xml:space="preserve">  Servicio</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2418,10 +2500,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="32" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2447,10 +2527,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="32" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2476,10 +2554,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="32" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2505,10 +2581,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="32" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2534,10 +2608,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="32" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2562,6 +2634,8 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
@@ -2570,17 +2644,19 @@
       </c>
       <c r="D14" s="19">
         <f>COUNTIF(F5:F12,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F14" s="19" t="n">
-        <v>6</v>
-      </c>
-    </row>
+      <c r="F14" s="19">
+        <f>COUNTIF(B5:B12,"?*")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
@@ -2588,13 +2664,17 @@
         </is>
       </c>
       <c r="B16" s="15" t="n"/>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="31" t="n"/>
       <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F16" s="15" t="n"/>
-    </row>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="21" t="inlineStr">
         <is>
@@ -2611,11 +2691,25 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-bar/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/04-tareas-perfiles.xlsx
@@ -14,10 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camarero Barra" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Head Bartender'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Head Bartender'!$A$1:$G$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Bartender'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Bartender'!$A$1:$G$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Barback'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Barback'!$A$1:$G$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Camarero Barra'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Camarero Barra'!$A$1:$G$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,8 +103,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -140,6 +159,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4EC"/>
         <bgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -213,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,6 +299,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -647,56 +743,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>04 — Tareas por Perfil · Bar / Cocktails</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Checklists específicos para cada perfil profesional.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>▸ Cada pestaña = un puesto de trabajo</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>▸ Perfecto para onboarding de personal nuevo</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="B8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+      <c r="B10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>▸ Estás en 04-tareas-perfiles.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="35" customHeight="1">
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -721,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -771,7 +1000,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -786,490 +1015,551 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pre-Servicio</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="31" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="n">
+      <c r="A6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Verificar mise en place completa de coctelería</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Preparar cócteles especiales del día / de la carta secreta</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="44" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Supervisar calibración de café (espresso test)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="44" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Briefing con equipo: cóctel del día, VIPs, eventos</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>16:45</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="44" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="n">
+      <c r="A10" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Verificar que la carta de cócteles está actualizada</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="43" t="n"/>
+      <c r="G10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="n"/>
+      <c r="B11" s="45" t="n"/>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="45" t="n"/>
+      <c r="G11" s="45" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  Servicio</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n"/>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="38" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Preparar cócteles premium y de alta complejidad</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="44" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="n">
+      <c r="A14" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>Supervisar calidad de cócteles preparados por el equipo</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="44" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>Atender a clientes VIP y regulares en barra</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="44" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>Recomendar cócteles según preferencias del cliente</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="44" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Controlar tiempos de preparación</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="41" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="F17" s="43" t="n"/>
+      <c r="G17" s="44" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="n"/>
+      <c r="B18" s="45" t="n"/>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="45" t="n"/>
+      <c r="G18" s="45" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre y Desarrollo</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="31" t="n"/>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="38" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="n">
+      <c r="A20" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>Supervisar cierre correcto de barra</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="44" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Desarrollar nuevas recetas y técnicas</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="44" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="n">
+      <c r="A22" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>Formar al equipo en nuevas técnicas</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="41" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>Semanal</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="44" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>Calcular coste de nuevos cócteles (escandallo)</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="41" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="42" t="inlineStr">
         <is>
           <t>Semanal</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
+      <c r="F23" s="43" t="n"/>
+      <c r="G23" s="44" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="47" t="n"/>
+      <c r="B24" s="48" t="n"/>
+      <c r="C24" s="41" t="n"/>
+      <c r="D24" s="42" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="44" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="47" t="n"/>
+      <c r="B25" s="48" t="n"/>
+      <c r="C25" s="41" t="n"/>
+      <c r="D25" s="42" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="F25" s="43" t="n"/>
+      <c r="G25" s="44" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D26" s="19">
-        <f>COUNTIF(F5:F24,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F26" s="19">
-        <f>COUNTIF(B5:B24,"?*")</f>
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="A26" s="47" t="n"/>
+      <c r="B26" s="48" t="n"/>
+      <c r="C26" s="41" t="n"/>
+      <c r="D26" s="42" t="n"/>
+      <c r="E26" s="42" t="n"/>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="44" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="47" t="n"/>
+      <c r="B27" s="48" t="n"/>
+      <c r="C27" s="41" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="44" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="31" t="n"/>
+      <c r="A28" s="47" t="n"/>
+      <c r="B28" s="48" t="n"/>
+      <c r="C28" s="41" t="n"/>
+      <c r="D28" s="42" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="44" t="n"/>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D30" s="19">
+        <f>COUNTIFS(B5:B28,"?*",F5:F28,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F30" s="19">
+        <f>COUNTIF(B5:B28,"?*")-COUNTIF(F5:F28,"N/A")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="30" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="31" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="F32:G32"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G24">
+  <conditionalFormatting sqref="A5:G28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1293,7 +1583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1343,7 +1633,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1358,490 +1648,551 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pre-Servicio</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="31" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="n">
+      <c r="A6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Preparar mise en place de su estación</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Cortar cítricos y preparar garnish</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="44" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Preparar jarabes del día</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="44" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Pulir cristalería de su zona</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="44" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="n">
+      <c r="A10" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Verificar stock de su speed rail</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="43" t="n"/>
+      <c r="G10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="n"/>
+      <c r="B11" s="45" t="n"/>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="45" t="n"/>
+      <c r="G11" s="45" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  Servicio</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n"/>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="38" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Preparar cócteles según carta y pedidos especiales</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="44" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="n">
+      <c r="A14" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>Servir cerveza de grifo y botella</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="44" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>Servir vinos por copa</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="44" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>Preparar cafés e infusiones</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="44" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Cobrar en barra (si el sistema lo permite)</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="43" t="n"/>
+      <c r="G17" s="44" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="n">
+      <c r="A18" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Mantener estación limpia y ordenada</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
-    </row>
-    <row r="19"/>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="44" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="n"/>
+      <c r="B19" s="45" t="n"/>
+      <c r="C19" s="45" t="n"/>
+      <c r="D19" s="45" t="n"/>
+      <c r="E19" s="45" t="n"/>
+      <c r="F19" s="45" t="n"/>
+      <c r="G19" s="45" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n"/>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="30" t="n"/>
-      <c r="G20" s="31" t="n"/>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="38" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Limpiar estación completa</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="44" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="n">
+      <c r="A22" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>Guardar mise en place en cámara</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="44" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>Lavar y guardar utensilios personales</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="42" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
+      <c r="F23" s="43" t="n"/>
+      <c r="G23" s="44" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="47" t="n"/>
+      <c r="B24" s="48" t="n"/>
+      <c r="C24" s="41" t="n"/>
+      <c r="D24" s="42" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="44" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="47" t="n"/>
+      <c r="B25" s="48" t="n"/>
+      <c r="C25" s="41" t="n"/>
+      <c r="D25" s="42" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="F25" s="43" t="n"/>
+      <c r="G25" s="44" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D26" s="19">
-        <f>COUNTIF(F5:F24,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F26" s="19">
-        <f>COUNTIF(B5:B24,"?*")</f>
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="A26" s="47" t="n"/>
+      <c r="B26" s="48" t="n"/>
+      <c r="C26" s="41" t="n"/>
+      <c r="D26" s="42" t="n"/>
+      <c r="E26" s="42" t="n"/>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="44" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="47" t="n"/>
+      <c r="B27" s="48" t="n"/>
+      <c r="C27" s="41" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="44" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="31" t="n"/>
+      <c r="A28" s="47" t="n"/>
+      <c r="B28" s="48" t="n"/>
+      <c r="C28" s="41" t="n"/>
+      <c r="D28" s="42" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="44" t="n"/>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D30" s="19">
+        <f>COUNTIFS(B5:B28,"?*",F5:F28,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F30" s="19">
+        <f>COUNTIF(B5:B28,"?*")-COUNTIF(F5:F28,"N/A")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="30" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="31" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G24">
+  <conditionalFormatting sqref="A5:G28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1865,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1915,7 +2266,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1930,448 +2281,501 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">  Soporte Continuo</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="31" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="n">
+      <c r="A6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Reponer hielo constantemente (antes de que pidan)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Reponer cristalería limpia en estaciones</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="44" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Recoger cristalería sucia de mesas y barra</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="44" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Lavar cristalería en lavavajillas de barra</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="44" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="n">
+      <c r="A10" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Reponer servilletas, pajitas y posavasos</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="F10" s="43" t="n"/>
+      <c r="G10" s="44" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="n">
+      <c r="A11" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Reponer botellas de speed rail desde bodega</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="43" t="n"/>
+      <c r="G11" s="44" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="n">
+      <c r="A12" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Reponer refrescos en cámara de barra</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="F12" s="43" t="n"/>
+      <c r="G12" s="44" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Mantener suelo limpio (secar derrames inmediatamente)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
-    </row>
-    <row r="14"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="44" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="n"/>
+      <c r="B14" s="45" t="n"/>
+      <c r="C14" s="45" t="n"/>
+      <c r="D14" s="45" t="n"/>
+      <c r="E14" s="45" t="n"/>
+      <c r="F14" s="45" t="n"/>
+      <c r="G14" s="45" t="n"/>
+    </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">  Limpieza</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n"/>
-      <c r="C15" s="30" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="31" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="37" t="n"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="38" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>Limpiar mesas y recoger vasos de zona de clientes</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="44" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Limpiar baños cada 2 horas (reponer jabón, papel)</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C17" s="41" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="42" t="inlineStr">
         <is>
           <t>Cada 2h</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="43" t="n"/>
+      <c r="G17" s="44" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="n">
+      <c r="A18" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Vaciar papeleras y ceniceros de terraza</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr">
+      <c r="C18" s="41" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="44" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="n">
+      <c r="A19" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>Barrer y fregar al cierre</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="41" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="43" t="n"/>
+      <c r="G19" s="44" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="n">
+      <c r="A20" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>Sacar basura y reciclar vidrio</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="44" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="47" t="n"/>
+      <c r="B21" s="48" t="n"/>
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="42" t="n"/>
+      <c r="E21" s="42" t="n"/>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="44" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="47" t="n"/>
+      <c r="B22" s="48" t="n"/>
+      <c r="C22" s="41" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="44" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D23" s="19">
-        <f>COUNTIF(F5:F21,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F23" s="19">
-        <f>COUNTIF(B5:B21,"?*")</f>
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="24"/>
+      <c r="A23" s="47" t="n"/>
+      <c r="B23" s="48" t="n"/>
+      <c r="C23" s="41" t="n"/>
+      <c r="D23" s="42" t="n"/>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="43" t="n"/>
+      <c r="G23" s="44" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="47" t="n"/>
+      <c r="B24" s="48" t="n"/>
+      <c r="C24" s="41" t="n"/>
+      <c r="D24" s="42" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="44" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="31" t="n"/>
+      <c r="A25" s="47" t="n"/>
+      <c r="B25" s="48" t="n"/>
+      <c r="C25" s="41" t="n"/>
+      <c r="D25" s="42" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="F25" s="43" t="n"/>
+      <c r="G25" s="44" t="n"/>
     </row>
     <row r="26"/>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D27" s="19">
+        <f>COUNTIFS(B5:B25,"?*",F5:F25,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F27" s="19">
+        <f>COUNTIF(B5:B25,"?*")-COUNTIF(F5:F25,"N/A")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="31" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B25:D25"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G21">
+  <conditionalFormatting sqref="A5:G25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2395,7 +2799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2445,7 +2849,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2460,244 +2864,289 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  Servicio</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="31" t="n"/>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="37" t="n"/>
+      <c r="D5" s="37" t="n"/>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="37" t="n"/>
+      <c r="G5" s="38" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="n">
+      <c r="A6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Atender mesas de sala y/o terraza</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="43" t="n"/>
+      <c r="G6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Tomar comandas con conocimiento de la carta de cócteles</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="44" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Servir bebidas desde barra a mesa</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="43" t="n"/>
+      <c r="G8" s="44" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Recomendar cócteles y maridajes</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="44" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="n">
+      <c r="A10" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Cobrar en mesa (datáfono portátil)</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="F10" s="43" t="n"/>
+      <c r="G10" s="44" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="n">
+      <c r="A11" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Recoger cristalería y mantener mesas limpias</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="41" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="42" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
-    </row>
-    <row r="12"/>
-    <row r="13"/>
+      <c r="F11" s="43" t="n"/>
+      <c r="G11" s="44" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="47" t="n"/>
+      <c r="B12" s="48" t="n"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="42" t="n"/>
+      <c r="E12" s="42" t="n"/>
+      <c r="F12" s="43" t="n"/>
+      <c r="G12" s="44" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="n"/>
+      <c r="B13" s="48" t="n"/>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="42" t="n"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="44" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D14" s="19">
-        <f>COUNTIF(F5:F12,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F14" s="19">
-        <f>COUNTIF(B5:B12,"?*")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="A14" s="47" t="n"/>
+      <c r="B14" s="48" t="n"/>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="42" t="n"/>
+      <c r="E14" s="42" t="n"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="n"/>
+      <c r="B15" s="48" t="n"/>
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="42" t="n"/>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="44" t="n"/>
+    </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="30" t="n"/>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="31" t="n"/>
+      <c r="A16" s="47" t="n"/>
+      <c r="B16" s="48" t="n"/>
+      <c r="C16" s="41" t="n"/>
+      <c r="D16" s="42" t="n"/>
+      <c r="E16" s="42" t="n"/>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="44" t="n"/>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D18" s="19">
+        <f>COUNTIFS(B5:B16,"?*",F5:F16,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F18" s="19">
+        <f>COUNTIF(B5:B16,"?*")-COUNTIF(F5:F16,"N/A")</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="31" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="6">
-    <mergeCell ref="F16:G16"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="F20:G20"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="B20:D20"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G12">
+  <conditionalFormatting sqref="A5:G16">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
